--- a/Fig.4(d).xlsx
+++ b/Fig.4(d).xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Superconductivity\Nb\Mn3Pt_Nb\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sachin\Research\Paper review\Mn3Pt_Nb\Dataset_2\New folder 2\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -360,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -943,7 +943,7 @@
         <v>31.25</v>
       </c>
       <c r="G25">
-        <v>5.4739999999999997E-2</v>
+        <v>5.475E-2</v>
       </c>
       <c r="H25">
         <v>31.25</v>
@@ -995,7 +995,7 @@
         <v>34.375</v>
       </c>
       <c r="G27">
-        <v>6.0229999999999999E-2</v>
+        <v>6.021E-2</v>
       </c>
       <c r="H27">
         <v>34.375</v>
@@ -1047,7 +1047,7 @@
         <v>37.5</v>
       </c>
       <c r="G29">
-        <v>6.5699999999999995E-2</v>
+        <v>6.5680000000000002E-2</v>
       </c>
       <c r="H29">
         <v>37.5</v>
@@ -1099,7 +1099,7 @@
         <v>40.625</v>
       </c>
       <c r="G31">
-        <v>7.1209999999999996E-2</v>
+        <v>7.1220000000000006E-2</v>
       </c>
       <c r="H31">
         <v>40.625</v>
@@ -1119,7 +1119,7 @@
         <v>42.1875</v>
       </c>
       <c r="E32">
-        <v>7.3950000000000002E-2</v>
+        <v>7.3959999999999998E-2</v>
       </c>
       <c r="F32">
         <v>42.1875</v>
@@ -1151,7 +1151,7 @@
         <v>43.75</v>
       </c>
       <c r="G33">
-        <v>7.6679999999999998E-2</v>
+        <v>7.6689999999999994E-2</v>
       </c>
       <c r="H33">
         <v>43.75</v>
@@ -1177,7 +1177,7 @@
         <v>45.3125</v>
       </c>
       <c r="G34">
-        <v>7.9420000000000004E-2</v>
+        <v>7.9399999999999998E-2</v>
       </c>
       <c r="H34">
         <v>45.3125</v>
@@ -1229,7 +1229,7 @@
         <v>48.4375</v>
       </c>
       <c r="G36">
-        <v>8.4930000000000005E-2</v>
+        <v>8.4919999999999995E-2</v>
       </c>
       <c r="H36">
         <v>48.4375</v>
@@ -1255,7 +1255,7 @@
         <v>50</v>
       </c>
       <c r="G37">
-        <v>8.7749999999999995E-2</v>
+        <v>8.7760000000000005E-2</v>
       </c>
       <c r="H37">
         <v>50</v>
@@ -1307,7 +1307,7 @@
         <v>53.125</v>
       </c>
       <c r="G39">
-        <v>9.3219999999999997E-2</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="H39">
         <v>53.125</v>
@@ -1333,7 +1333,7 @@
         <v>54.6875</v>
       </c>
       <c r="G40">
-        <v>9.5979999999999996E-2</v>
+        <v>9.5960000000000004E-2</v>
       </c>
       <c r="H40">
         <v>54.6875</v>
@@ -1359,7 +1359,7 @@
         <v>56.25</v>
       </c>
       <c r="G41">
-        <v>9.869E-2</v>
+        <v>9.8659999999999998E-2</v>
       </c>
       <c r="H41">
         <v>56.25</v>
@@ -1385,7 +1385,7 @@
         <v>57.8125</v>
       </c>
       <c r="G42">
-        <v>0.10145</v>
+        <v>0.10145999999999999</v>
       </c>
       <c r="H42">
         <v>57.8125</v>
@@ -1437,7 +1437,7 @@
         <v>60.9375</v>
       </c>
       <c r="G44">
-        <v>0.10692</v>
+        <v>0.10691000000000001</v>
       </c>
       <c r="H44">
         <v>60.9375</v>
@@ -1463,7 +1463,7 @@
         <v>62.5</v>
       </c>
       <c r="G45">
-        <v>0.10967</v>
+        <v>0.10968</v>
       </c>
       <c r="H45">
         <v>62.5</v>
@@ -1489,7 +1489,7 @@
         <v>64.0625</v>
       </c>
       <c r="G46">
-        <v>0.11243</v>
+        <v>0.11244</v>
       </c>
       <c r="H46">
         <v>64.0625</v>
@@ -1515,7 +1515,7 @@
         <v>65.625</v>
       </c>
       <c r="G47">
-        <v>0.11518</v>
+        <v>0.11521000000000001</v>
       </c>
       <c r="H47">
         <v>65.625</v>
@@ -1541,7 +1541,7 @@
         <v>67.1875</v>
       </c>
       <c r="G48">
-        <v>0.1179</v>
+        <v>0.1181</v>
       </c>
       <c r="H48">
         <v>67.1875</v>
@@ -1593,7 +1593,7 @@
         <v>70.3125</v>
       </c>
       <c r="G50">
-        <v>0.12336999999999999</v>
+        <v>0.12339</v>
       </c>
       <c r="H50">
         <v>70.3125</v>
@@ -1619,7 +1619,7 @@
         <v>71.875</v>
       </c>
       <c r="G51">
-        <v>0.12612000000000001</v>
+        <v>0.12611</v>
       </c>
       <c r="H51">
         <v>71.875</v>
@@ -1645,7 +1645,7 @@
         <v>73.4375</v>
       </c>
       <c r="G52">
-        <v>0.12886</v>
+        <v>0.12887999999999999</v>
       </c>
       <c r="H52">
         <v>73.4375</v>
@@ -1697,7 +1697,7 @@
         <v>76.5625</v>
       </c>
       <c r="G54">
-        <v>0.13433</v>
+        <v>0.13431999999999999</v>
       </c>
       <c r="H54">
         <v>76.5625</v>
@@ -1723,7 +1723,7 @@
         <v>78.125</v>
       </c>
       <c r="G55">
-        <v>0.13708000000000001</v>
+        <v>0.1371</v>
       </c>
       <c r="H55">
         <v>78.125</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>0.13950000000000001</v>
+        <v>0.14258000000000001</v>
       </c>
       <c r="B57">
-        <v>79.6875</v>
+        <v>81.25</v>
       </c>
       <c r="C57">
         <v>0.13958000000000001</v>
@@ -1775,7 +1775,7 @@
         <v>79.6875</v>
       </c>
       <c r="G57">
-        <v>0.13950000000000001</v>
+        <v>0.1396</v>
       </c>
       <c r="H57">
         <v>79.6875</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>0.13675999999999999</v>
+        <v>0.14529</v>
       </c>
       <c r="B58">
-        <v>78.125</v>
+        <v>82.8125</v>
       </c>
       <c r="C58">
         <v>0.1368</v>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>0.13403000000000001</v>
+        <v>0.14804999999999999</v>
       </c>
       <c r="B59">
-        <v>76.5625</v>
+        <v>84.375</v>
       </c>
       <c r="C59">
         <v>0.13406999999999999</v>
@@ -1827,7 +1827,7 @@
         <v>76.5625</v>
       </c>
       <c r="G59">
-        <v>0.13400999999999999</v>
+        <v>0.13402</v>
       </c>
       <c r="H59">
         <v>76.5625</v>
@@ -1835,10 +1835,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>0.13127</v>
+        <v>0.15079999999999999</v>
       </c>
       <c r="B60">
-        <v>75</v>
+        <v>85.9375</v>
       </c>
       <c r="C60">
         <v>0.13134000000000001</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>0.12856000000000001</v>
+        <v>0.15357999999999999</v>
       </c>
       <c r="B61">
-        <v>73.4375</v>
+        <v>87.5</v>
       </c>
       <c r="C61">
         <v>0.12859999999999999</v>
@@ -1879,7 +1879,7 @@
         <v>73.4375</v>
       </c>
       <c r="G61">
-        <v>0.12853999999999999</v>
+        <v>0.12855</v>
       </c>
       <c r="H61">
         <v>73.4375</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>0.12578</v>
+        <v>0.15634000000000001</v>
       </c>
       <c r="B62">
-        <v>71.875</v>
+        <v>89.0625</v>
       </c>
       <c r="C62">
         <v>0.12587000000000001</v>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>0.12307</v>
+        <v>0.15909000000000001</v>
       </c>
       <c r="B63">
-        <v>70.3125</v>
+        <v>90.625</v>
       </c>
       <c r="C63">
         <v>0.12311</v>
@@ -1931,7 +1931,7 @@
         <v>70.3125</v>
       </c>
       <c r="G63">
-        <v>0.12304</v>
+        <v>0.12302</v>
       </c>
       <c r="H63">
         <v>70.3125</v>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>0.12031</v>
+        <v>0.16184999999999999</v>
       </c>
       <c r="B64">
-        <v>68.75</v>
+        <v>92.1875</v>
       </c>
       <c r="C64">
         <v>0.12037</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>0.11758</v>
+        <v>0.16458</v>
       </c>
       <c r="B65">
-        <v>67.1875</v>
+        <v>93.75</v>
       </c>
       <c r="C65">
         <v>0.11763999999999999</v>
@@ -1983,7 +1983,7 @@
         <v>67.1875</v>
       </c>
       <c r="G65">
-        <v>0.11755</v>
+        <v>0.11756</v>
       </c>
       <c r="H65">
         <v>67.1875</v>
@@ -1991,10 +1991,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>0.11484</v>
+        <v>0.16733999999999999</v>
       </c>
       <c r="B66">
-        <v>65.625</v>
+        <v>95.3125</v>
       </c>
       <c r="C66">
         <v>0.11488</v>
@@ -2009,7 +2009,7 @@
         <v>65.625</v>
       </c>
       <c r="G66">
-        <v>0.11482000000000001</v>
+        <v>0.11481</v>
       </c>
       <c r="H66">
         <v>65.625</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>0.11211</v>
+        <v>0.1701</v>
       </c>
       <c r="B67">
-        <v>64.0625</v>
+        <v>96.875</v>
       </c>
       <c r="C67">
         <v>0.11212999999999999</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>0.10931</v>
+        <v>0.17285</v>
       </c>
       <c r="B68">
-        <v>62.5</v>
+        <v>98.4375</v>
       </c>
       <c r="C68">
         <v>0.10936999999999999</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>0.10661</v>
+        <v>0.17529</v>
       </c>
       <c r="B69">
-        <v>60.9375</v>
+        <v>100</v>
       </c>
       <c r="C69">
         <v>0.10661</v>
@@ -2081,7 +2081,7 @@
         <v>60.9375</v>
       </c>
       <c r="E69">
-        <v>0.10657</v>
+        <v>0.10657999999999999</v>
       </c>
       <c r="F69">
         <v>60.9375</v>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>0.10384</v>
+        <v>0.17252999999999999</v>
       </c>
       <c r="B70">
-        <v>59.375</v>
+        <v>98.4375</v>
       </c>
       <c r="C70">
         <v>0.10388</v>
@@ -2107,7 +2107,7 @@
         <v>59.375</v>
       </c>
       <c r="E70">
-        <v>0.10384</v>
+        <v>0.10382</v>
       </c>
       <c r="F70">
         <v>59.375</v>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>0.10112</v>
+        <v>0.16979</v>
       </c>
       <c r="B71">
-        <v>57.8125</v>
+        <v>96.875</v>
       </c>
       <c r="C71">
         <v>0.10113999999999999</v>
@@ -2133,7 +2133,7 @@
         <v>57.8125</v>
       </c>
       <c r="E71">
-        <v>0.10108</v>
+        <v>0.10105</v>
       </c>
       <c r="F71">
         <v>57.8125</v>
@@ -2147,10 +2147,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>9.8369999999999999E-2</v>
+        <v>0.16702</v>
       </c>
       <c r="B72">
-        <v>56.25</v>
+        <v>95.3125</v>
       </c>
       <c r="C72">
         <v>9.8409999999999997E-2</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>9.5649999999999999E-2</v>
+        <v>0.1643</v>
       </c>
       <c r="B73">
-        <v>54.6875</v>
+        <v>93.75</v>
       </c>
       <c r="C73">
         <v>9.5649999999999999E-2</v>
@@ -2191,7 +2191,7 @@
         <v>54.6875</v>
       </c>
       <c r="G73">
-        <v>9.5610000000000001E-2</v>
+        <v>9.5600000000000004E-2</v>
       </c>
       <c r="H73">
         <v>54.6875</v>
@@ -2199,10 +2199,10 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>9.2899999999999996E-2</v>
+        <v>0.1615</v>
       </c>
       <c r="B74">
-        <v>53.125</v>
+        <v>92.1875</v>
       </c>
       <c r="C74">
         <v>9.2920000000000003E-2</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>9.0160000000000004E-2</v>
+        <v>0.15876999999999999</v>
       </c>
       <c r="B75">
-        <v>51.5625</v>
+        <v>90.625</v>
       </c>
       <c r="C75">
         <v>9.0179999999999996E-2</v>
@@ -2243,7 +2243,7 @@
         <v>51.5625</v>
       </c>
       <c r="G75">
-        <v>9.0120000000000006E-2</v>
+        <v>9.0109999999999996E-2</v>
       </c>
       <c r="H75">
         <v>51.5625</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>8.7340000000000001E-2</v>
+        <v>0.15598999999999999</v>
       </c>
       <c r="B76">
-        <v>50</v>
+        <v>89.0625</v>
       </c>
       <c r="C76" s="1">
         <v>8.7359999999999993E-2</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>8.4610000000000005E-2</v>
+        <v>0.15326000000000001</v>
       </c>
       <c r="B77">
-        <v>48.4375</v>
+        <v>87.5</v>
       </c>
       <c r="C77">
         <v>8.4610000000000005E-2</v>
@@ -2295,7 +2295,7 @@
         <v>48.4375</v>
       </c>
       <c r="G77">
-        <v>8.4540000000000004E-2</v>
+        <v>8.455E-2</v>
       </c>
       <c r="H77">
         <v>48.4375</v>
@@ -2303,10 +2303,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>8.1850000000000006E-2</v>
+        <v>0.15048</v>
       </c>
       <c r="B78">
-        <v>46.875</v>
+        <v>85.9375</v>
       </c>
       <c r="C78">
         <v>8.1869999999999998E-2</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>7.9140000000000002E-2</v>
+        <v>0.14774000000000001</v>
       </c>
       <c r="B79">
-        <v>45.3125</v>
+        <v>84.375</v>
       </c>
       <c r="C79" s="1">
         <v>7.9089999999999994E-2</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>7.6380000000000003E-2</v>
+        <v>0.14499000000000001</v>
       </c>
       <c r="B80">
-        <v>43.75</v>
+        <v>82.8125</v>
       </c>
       <c r="C80" s="1">
         <v>7.6399999999999996E-2</v>
@@ -2373,7 +2373,7 @@
         <v>43.75</v>
       </c>
       <c r="G80">
-        <v>7.6319999999999999E-2</v>
+        <v>7.6350000000000001E-2</v>
       </c>
       <c r="H80">
         <v>43.75</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>7.3649999999999993E-2</v>
+        <v>0.14227000000000001</v>
       </c>
       <c r="B81">
-        <v>42.1875</v>
+        <v>81.25</v>
       </c>
       <c r="C81" s="1">
         <v>7.3649999999999993E-2</v>
@@ -2399,7 +2399,7 @@
         <v>42.1875</v>
       </c>
       <c r="G81">
-        <v>7.3580000000000007E-2</v>
+        <v>7.356E-2</v>
       </c>
       <c r="H81">
         <v>42.1875</v>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>7.0889999999999995E-2</v>
+        <v>0.13950000000000001</v>
       </c>
       <c r="B82">
-        <v>40.625</v>
+        <v>79.6875</v>
       </c>
       <c r="C82" s="1">
         <v>7.0889999999999995E-2</v>
@@ -2425,7 +2425,7 @@
         <v>40.625</v>
       </c>
       <c r="G82">
-        <v>7.0830000000000004E-2</v>
+        <v>7.0860000000000006E-2</v>
       </c>
       <c r="H82">
         <v>40.625</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>6.8180000000000004E-2</v>
+        <v>0.13675999999999999</v>
       </c>
       <c r="B83">
-        <v>39.0625</v>
+        <v>78.125</v>
       </c>
       <c r="C83">
         <v>6.8129999999999996E-2</v>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>6.54E-2</v>
+        <v>0.13403000000000001</v>
       </c>
       <c r="B84">
-        <v>37.5</v>
+        <v>76.5625</v>
       </c>
       <c r="C84">
         <v>6.54E-2</v>
@@ -2477,7 +2477,7 @@
         <v>37.5</v>
       </c>
       <c r="G84">
-        <v>6.5329999999999999E-2</v>
+        <v>6.5320000000000003E-2</v>
       </c>
       <c r="H84">
         <v>37.5</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>6.2689999999999996E-2</v>
+        <v>0.13127</v>
       </c>
       <c r="B85">
-        <v>35.9375</v>
+        <v>75</v>
       </c>
       <c r="C85">
         <v>6.2640000000000001E-2</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>5.9909999999999998E-2</v>
+        <v>0.12856000000000001</v>
       </c>
       <c r="B86">
-        <v>34.375</v>
+        <v>73.4375</v>
       </c>
       <c r="C86">
         <v>5.9889999999999999E-2</v>
@@ -2529,7 +2529,7 @@
         <v>34.375</v>
       </c>
       <c r="G86">
-        <v>5.9839999999999997E-2</v>
+        <v>5.9819999999999998E-2</v>
       </c>
       <c r="H86">
         <v>34.375</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>5.7169999999999999E-2</v>
+        <v>0.12578</v>
       </c>
       <c r="B87">
-        <v>32.8125</v>
+        <v>71.875</v>
       </c>
       <c r="C87">
         <v>5.7169999999999999E-2</v>
@@ -2555,7 +2555,7 @@
         <v>32.8125</v>
       </c>
       <c r="G87">
-        <v>5.7110000000000001E-2</v>
+        <v>5.7119999999999997E-2</v>
       </c>
       <c r="H87">
         <v>32.8125</v>
@@ -2563,10 +2563,10 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>5.416E-2</v>
+        <v>0.12307</v>
       </c>
       <c r="B88">
-        <v>31.25</v>
+        <v>70.3125</v>
       </c>
       <c r="C88">
         <v>5.4420000000000003E-2</v>
@@ -2581,7 +2581,7 @@
         <v>31.25</v>
       </c>
       <c r="G88">
-        <v>5.4350000000000002E-2</v>
+        <v>5.4339999999999999E-2</v>
       </c>
       <c r="H88">
         <v>31.25</v>
@@ -2589,10 +2589,10 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>5.0070000000000003E-2</v>
+        <v>0.12031</v>
       </c>
       <c r="B89">
-        <v>29.6875</v>
+        <v>68.75</v>
       </c>
       <c r="C89">
         <v>5.1700000000000003E-2</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>4.3580000000000001E-2</v>
+        <v>0.11758</v>
       </c>
       <c r="B90">
-        <v>28.125</v>
+        <v>67.1875</v>
       </c>
       <c r="C90">
         <v>4.895E-2</v>
@@ -2633,7 +2633,7 @@
         <v>28.125</v>
       </c>
       <c r="G90">
-        <v>4.888E-2</v>
+        <v>4.8860000000000001E-2</v>
       </c>
       <c r="H90">
         <v>28.125</v>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>1.3440000000000001E-2</v>
+        <v>0.11484</v>
       </c>
       <c r="B91">
-        <v>26.5625</v>
+        <v>65.625</v>
       </c>
       <c r="C91">
         <v>4.6100000000000002E-2</v>
@@ -2659,7 +2659,7 @@
         <v>26.5625</v>
       </c>
       <c r="G91">
-        <v>4.6149999999999997E-2</v>
+        <v>4.614E-2</v>
       </c>
       <c r="H91">
         <v>26.5625</v>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>0</v>
+        <v>0.11211</v>
       </c>
       <c r="B92">
-        <v>25</v>
+        <v>64.0625</v>
       </c>
       <c r="C92">
         <v>4.292E-2</v>
@@ -2685,7 +2685,7 @@
         <v>25</v>
       </c>
       <c r="G92">
-        <v>4.3409999999999997E-2</v>
+        <v>4.342E-2</v>
       </c>
       <c r="H92">
         <v>25</v>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>0</v>
+        <v>0.10931</v>
       </c>
       <c r="B93">
-        <v>23.4375</v>
+        <v>62.5</v>
       </c>
       <c r="C93">
         <v>3.8870000000000002E-2</v>
@@ -2711,7 +2711,7 @@
         <v>23.4375</v>
       </c>
       <c r="G93">
-        <v>4.0660000000000002E-2</v>
+        <v>4.0649999999999999E-2</v>
       </c>
       <c r="H93">
         <v>23.4375</v>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>0</v>
+        <v>0.10661</v>
       </c>
       <c r="B94">
-        <v>21.875</v>
+        <v>60.9375</v>
       </c>
       <c r="C94" s="1">
         <v>3.3419999999999998E-2</v>
@@ -2737,7 +2737,7 @@
         <v>21.875</v>
       </c>
       <c r="G94">
-        <v>3.7859999999999998E-2</v>
+        <v>3.7850000000000002E-2</v>
       </c>
       <c r="H94">
         <v>21.875</v>
@@ -2745,10 +2745,10 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>0</v>
+        <v>0.10384</v>
       </c>
       <c r="B95">
-        <v>20.3125</v>
+        <v>59.375</v>
       </c>
       <c r="C95" s="1">
         <v>2.5649999999999999E-2</v>
@@ -2763,7 +2763,7 @@
         <v>20.3125</v>
       </c>
       <c r="G95">
-        <v>3.4909999999999997E-2</v>
+        <v>3.492E-2</v>
       </c>
       <c r="H95">
         <v>20.3125</v>
@@ -2771,10 +2771,10 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>0</v>
+        <v>0.10112</v>
       </c>
       <c r="B96">
-        <v>18.75</v>
+        <v>57.8125</v>
       </c>
       <c r="C96" s="1">
         <v>2.15E-3</v>
@@ -2783,7 +2783,7 @@
         <v>18.75</v>
       </c>
       <c r="E96">
-        <v>3.1370000000000002E-2</v>
+        <v>3.1390000000000001E-2</v>
       </c>
       <c r="F96">
         <v>18.75</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>0</v>
+        <v>9.8369999999999999E-2</v>
       </c>
       <c r="B97">
-        <v>17.1875</v>
+        <v>56.25</v>
       </c>
       <c r="C97" s="1">
         <v>0</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>0</v>
+        <v>9.5649999999999999E-2</v>
       </c>
       <c r="B98">
-        <v>15.625</v>
+        <v>54.6875</v>
       </c>
       <c r="C98" s="1">
         <v>0</v>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>0</v>
+        <v>9.2899999999999996E-2</v>
       </c>
       <c r="B99">
-        <v>14.0625</v>
+        <v>53.125</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>0</v>
+        <v>9.0160000000000004E-2</v>
       </c>
       <c r="B100">
-        <v>12.5</v>
+        <v>51.5625</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>0</v>
+        <v>8.7340000000000001E-2</v>
       </c>
       <c r="B101">
-        <v>10.9375</v>
+        <v>50</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>0</v>
+        <v>8.4610000000000005E-2</v>
       </c>
       <c r="B102">
-        <v>9.375</v>
+        <v>48.4375</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>9.375</v>
       </c>
       <c r="G102" s="1">
-        <v>7.7522099999999998E-4</v>
+        <v>6.8336600000000003E-4</v>
       </c>
       <c r="H102">
         <v>9.375</v>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>0</v>
+        <v>8.1850000000000006E-2</v>
       </c>
       <c r="B103">
-        <v>7.8125</v>
+        <v>46.875</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>7.8125</v>
       </c>
       <c r="G103" s="1">
-        <v>1.7227099999999999E-4</v>
+        <v>2.57853E-4</v>
       </c>
       <c r="H103">
         <v>7.8125</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>0</v>
+        <v>7.9140000000000002E-2</v>
       </c>
       <c r="B104">
-        <v>6.25</v>
+        <v>45.3125</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2997,7 +2997,7 @@
         <v>6.25</v>
       </c>
       <c r="G104" s="1">
-        <v>4.3067800000000001E-5</v>
+        <v>3.3513000000000003E-5</v>
       </c>
       <c r="H104">
         <v>6.25</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>0</v>
+        <v>7.6380000000000003E-2</v>
       </c>
       <c r="B105">
-        <v>4.6875</v>
+        <v>43.75</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>0</v>
+        <v>7.3649999999999993E-2</v>
       </c>
       <c r="B106">
-        <v>3.125</v>
+        <v>42.1875</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -3057,10 +3057,10 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>0</v>
+        <v>7.0889999999999995E-2</v>
       </c>
       <c r="B107">
-        <v>1.5625</v>
+        <v>40.625</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>0</v>
+        <v>6.8180000000000004E-2</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>39.0625</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>0</v>
+        <v>6.54E-2</v>
       </c>
       <c r="B109">
-        <v>-1.5625</v>
+        <v>37.5</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>0</v>
+        <v>6.2689999999999996E-2</v>
       </c>
       <c r="B110">
-        <v>-3.125</v>
+        <v>35.9375</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -3161,10 +3161,10 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>0</v>
+        <v>5.9909999999999998E-2</v>
       </c>
       <c r="B111">
-        <v>-4.6875</v>
+        <v>34.375</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -3187,10 +3187,10 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>0</v>
+        <v>5.7169999999999999E-2</v>
       </c>
       <c r="B112">
-        <v>-6.25</v>
+        <v>32.8125</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>0</v>
+        <v>5.416E-2</v>
       </c>
       <c r="B113">
-        <v>-7.8125</v>
+        <v>31.25</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>0</v>
+        <v>5.0070000000000003E-2</v>
       </c>
       <c r="B114">
-        <v>-9.375</v>
+        <v>29.6875</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>0</v>
+        <v>4.3580000000000001E-2</v>
       </c>
       <c r="B115">
-        <v>-10.9375</v>
+        <v>28.125</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>0</v>
+        <v>1.3440000000000001E-2</v>
       </c>
       <c r="B116">
-        <v>-12.5</v>
+        <v>26.5625</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="B117">
-        <v>-14.0625</v>
+        <v>25</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="B118">
-        <v>-15.625</v>
+        <v>23.4375</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="B119">
-        <v>-17.1875</v>
+        <v>21.875</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="B120">
-        <v>-18.75</v>
+        <v>20.3125</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="B121">
-        <v>-20.3125</v>
+        <v>18.75</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -3450,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="B122">
-        <v>-21.875</v>
+        <v>17.1875</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="B123">
-        <v>-23.4375</v>
+        <v>15.625</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -3491,7 +3491,7 @@
         <v>-23.4375</v>
       </c>
       <c r="G123">
-        <v>-4.0590000000000001E-2</v>
+        <v>-4.061E-2</v>
       </c>
       <c r="H123">
         <v>-23.4375</v>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="B124">
-        <v>-25</v>
+        <v>14.0625</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>-25</v>
       </c>
       <c r="G124">
-        <v>-4.367E-2</v>
+        <v>-4.3679999999999997E-2</v>
       </c>
       <c r="H124">
         <v>-25</v>
@@ -3528,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="B125">
-        <v>-26.5625</v>
+        <v>12.5</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -3554,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="B126">
-        <v>-28.125</v>
+        <v>10.9375</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         <v>-28.125</v>
       </c>
       <c r="G126">
-        <v>-4.9230000000000003E-2</v>
+        <v>-4.922E-2</v>
       </c>
       <c r="H126">
         <v>-28.125</v>
@@ -3580,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="B127">
-        <v>-29.6875</v>
+        <v>9.375</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>-29.6875</v>
       </c>
       <c r="G127">
-        <v>-5.1950000000000003E-2</v>
+        <v>-5.1959999999999999E-2</v>
       </c>
       <c r="H127">
         <v>-29.6875</v>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="B128">
-        <v>-31.25</v>
+        <v>7.8125</v>
       </c>
       <c r="C128" s="1">
         <v>-8.6135699999999996E-5</v>
@@ -3621,7 +3621,7 @@
         <v>-31.25</v>
       </c>
       <c r="G128">
-        <v>-5.4719999999999998E-2</v>
+        <v>-5.475E-2</v>
       </c>
       <c r="H128">
         <v>-31.25</v>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="B129">
-        <v>-32.8125</v>
+        <v>6.25</v>
       </c>
       <c r="C129">
         <v>-4.24E-2</v>
@@ -3658,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="B130">
-        <v>-34.375</v>
+        <v>4.6875</v>
       </c>
       <c r="C130">
         <v>-6.019E-2</v>
@@ -3673,7 +3673,7 @@
         <v>-34.375</v>
       </c>
       <c r="G130">
-        <v>-6.021E-2</v>
+        <v>-6.0220000000000003E-2</v>
       </c>
       <c r="H130">
         <v>-34.375</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="B131">
-        <v>-35.9375</v>
+        <v>3.125</v>
       </c>
       <c r="C131">
         <v>-6.2920000000000004E-2</v>
@@ -3699,7 +3699,7 @@
         <v>-35.9375</v>
       </c>
       <c r="G131">
-        <v>-6.2920000000000004E-2</v>
+        <v>-6.293E-2</v>
       </c>
       <c r="H131">
         <v>-35.9375</v>
@@ -3710,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="B132">
-        <v>-37.5</v>
+        <v>1.5625</v>
       </c>
       <c r="C132">
         <v>-6.5680000000000002E-2</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="B133">
-        <v>-39.0625</v>
+        <v>0</v>
       </c>
       <c r="C133">
         <v>-6.8430000000000005E-2</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="B134">
-        <v>-40.625</v>
+        <v>-1.5625</v>
       </c>
       <c r="C134">
         <v>-7.1190000000000003E-2</v>
@@ -3777,7 +3777,7 @@
         <v>-40.625</v>
       </c>
       <c r="G134">
-        <v>-7.1169999999999997E-2</v>
+        <v>-7.1150000000000005E-2</v>
       </c>
       <c r="H134">
         <v>-40.625</v>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="B135">
-        <v>-42.1875</v>
+        <v>-3.125</v>
       </c>
       <c r="C135">
         <v>-7.3929999999999996E-2</v>
@@ -3814,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="B136">
-        <v>-43.75</v>
+        <v>-4.6875</v>
       </c>
       <c r="C136">
         <v>-7.6660000000000006E-2</v>
@@ -3829,7 +3829,7 @@
         <v>-43.75</v>
       </c>
       <c r="G136">
-        <v>-7.6660000000000006E-2</v>
+        <v>-7.6670000000000002E-2</v>
       </c>
       <c r="H136">
         <v>-43.75</v>
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="B137">
-        <v>-45.3125</v>
+        <v>-6.25</v>
       </c>
       <c r="C137">
         <v>-7.9399999999999998E-2</v>
@@ -3855,7 +3855,7 @@
         <v>-45.3125</v>
       </c>
       <c r="G137">
-        <v>-7.9420000000000004E-2</v>
+        <v>-7.9439999999999997E-2</v>
       </c>
       <c r="H137">
         <v>-45.3125</v>
@@ -3863,10 +3863,10 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>-1.0767E-4</v>
+        <v>0</v>
       </c>
       <c r="B138">
-        <v>-46.875</v>
+        <v>-7.8125</v>
       </c>
       <c r="C138">
         <v>-8.2150000000000001E-2</v>
@@ -3881,7 +3881,7 @@
         <v>-46.875</v>
       </c>
       <c r="G138">
-        <v>-8.2150000000000001E-2</v>
+        <v>-8.2140000000000005E-2</v>
       </c>
       <c r="H138">
         <v>-46.875</v>
@@ -3889,10 +3889,10 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>-8.3750000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="B139">
-        <v>-48.4375</v>
+        <v>-9.375</v>
       </c>
       <c r="C139">
         <v>-8.4870000000000001E-2</v>
@@ -3907,7 +3907,7 @@
         <v>-48.4375</v>
       </c>
       <c r="G139">
-        <v>-8.4909999999999999E-2</v>
+        <v>-8.4919999999999995E-2</v>
       </c>
       <c r="H139">
         <v>-48.4375</v>
@@ -3915,10 +3915,10 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>-8.7660000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="B140">
-        <v>-50</v>
+        <v>-10.9375</v>
       </c>
       <c r="C140">
         <v>-8.7709999999999996E-2</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>-9.042E-2</v>
+        <v>0</v>
       </c>
       <c r="B141">
-        <v>-51.5625</v>
+        <v>-12.5</v>
       </c>
       <c r="C141">
         <v>-9.0440000000000006E-2</v>
@@ -3967,10 +3967,10 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>-9.3160000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="B142">
-        <v>-53.125</v>
+        <v>-14.0625</v>
       </c>
       <c r="C142">
         <v>-9.3200000000000005E-2</v>
@@ -3985,7 +3985,7 @@
         <v>-53.125</v>
       </c>
       <c r="G142">
-        <v>-9.3200000000000005E-2</v>
+        <v>-9.3219999999999997E-2</v>
       </c>
       <c r="H142">
         <v>-53.125</v>
@@ -3993,10 +3993,10 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>-9.5909999999999995E-2</v>
+        <v>0</v>
       </c>
       <c r="B143">
-        <v>-54.6875</v>
+        <v>-15.625</v>
       </c>
       <c r="C143">
         <v>-9.5930000000000001E-2</v>
@@ -4011,7 +4011,7 @@
         <v>-54.6875</v>
       </c>
       <c r="G143">
-        <v>-9.5960000000000004E-2</v>
+        <v>-9.597E-2</v>
       </c>
       <c r="H143">
         <v>-54.6875</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>-9.8650000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="B144">
-        <v>-56.25</v>
+        <v>-17.1875</v>
       </c>
       <c r="C144">
         <v>-9.869E-2</v>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>-0.1014</v>
+        <v>0</v>
       </c>
       <c r="B145">
-        <v>-57.8125</v>
+        <v>-18.75</v>
       </c>
       <c r="C145">
         <v>-0.10142</v>
@@ -4063,7 +4063,7 @@
         <v>-57.8125</v>
       </c>
       <c r="G145">
-        <v>-0.10145</v>
+        <v>-0.10144</v>
       </c>
       <c r="H145">
         <v>-57.8125</v>
@@ -4071,10 +4071,10 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>-0.10414</v>
+        <v>0</v>
       </c>
       <c r="B146">
-        <v>-59.375</v>
+        <v>-20.3125</v>
       </c>
       <c r="C146">
         <v>-0.10417999999999999</v>
@@ -4097,10 +4097,10 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>-0.10689</v>
+        <v>0</v>
       </c>
       <c r="B147">
-        <v>-60.9375</v>
+        <v>-21.875</v>
       </c>
       <c r="C147">
         <v>-0.10692</v>
@@ -4115,7 +4115,7 @@
         <v>-60.9375</v>
       </c>
       <c r="G147">
-        <v>-0.10693999999999999</v>
+        <v>-0.10695</v>
       </c>
       <c r="H147">
         <v>-60.9375</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>-0.10963000000000001</v>
+        <v>0</v>
       </c>
       <c r="B148">
-        <v>-62.5</v>
+        <v>-23.4375</v>
       </c>
       <c r="C148">
         <v>-0.10967</v>
@@ -4141,7 +4141,7 @@
         <v>-62.5</v>
       </c>
       <c r="G148">
-        <v>-0.10967</v>
+        <v>-0.10965999999999999</v>
       </c>
       <c r="H148">
         <v>-62.5</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>-0.11239</v>
+        <v>0</v>
       </c>
       <c r="B149">
-        <v>-64.0625</v>
+        <v>-25</v>
       </c>
       <c r="C149">
         <v>-0.11243</v>
@@ -4175,10 +4175,10 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>-0.11514000000000001</v>
+        <v>0</v>
       </c>
       <c r="B150">
-        <v>-65.625</v>
+        <v>-26.5625</v>
       </c>
       <c r="C150">
         <v>-0.11516</v>
@@ -4193,7 +4193,7 @@
         <v>-65.625</v>
       </c>
       <c r="G150">
-        <v>-0.11516</v>
+        <v>-0.11516999999999999</v>
       </c>
       <c r="H150">
         <v>-65.625</v>
@@ -4201,10 +4201,10 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>-0.11788</v>
+        <v>0</v>
       </c>
       <c r="B151">
-        <v>-67.1875</v>
+        <v>-28.125</v>
       </c>
       <c r="C151">
         <v>-0.1179</v>
@@ -4219,7 +4219,7 @@
         <v>-67.1875</v>
       </c>
       <c r="G151">
-        <v>-0.11794</v>
+        <v>-0.11796</v>
       </c>
       <c r="H151">
         <v>-67.1875</v>
@@ -4227,10 +4227,10 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>-0.12063</v>
+        <v>0</v>
       </c>
       <c r="B152">
-        <v>-68.75</v>
+        <v>-29.6875</v>
       </c>
       <c r="C152">
         <v>-0.12063</v>
@@ -4245,7 +4245,7 @@
         <v>-68.75</v>
       </c>
       <c r="G152">
-        <v>-0.12068</v>
+        <v>-0.12067</v>
       </c>
       <c r="H152">
         <v>-68.75</v>
@@ -4253,10 +4253,10 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>-0.12339</v>
+        <v>0</v>
       </c>
       <c r="B153">
-        <v>-70.3125</v>
+        <v>-31.25</v>
       </c>
       <c r="C153">
         <v>-0.12339</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>-0.12612000000000001</v>
+        <v>0</v>
       </c>
       <c r="B154">
-        <v>-71.875</v>
+        <v>-32.8125</v>
       </c>
       <c r="C154">
         <v>-0.12612000000000001</v>
@@ -4297,7 +4297,7 @@
         <v>-71.875</v>
       </c>
       <c r="G154">
-        <v>-0.12617</v>
+        <v>-0.12619</v>
       </c>
       <c r="H154">
         <v>-71.875</v>
@@ -4305,10 +4305,10 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>-0.12887999999999999</v>
+        <v>0</v>
       </c>
       <c r="B155">
-        <v>-73.4375</v>
+        <v>-34.375</v>
       </c>
       <c r="C155">
         <v>-0.12887999999999999</v>
@@ -4317,7 +4317,7 @@
         <v>-73.4375</v>
       </c>
       <c r="E155">
-        <v>-0.12892000000000001</v>
+        <v>-0.12891</v>
       </c>
       <c r="F155">
         <v>-73.4375</v>
@@ -4331,10 +4331,10 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>-0.13161999999999999</v>
+        <v>0</v>
       </c>
       <c r="B156">
-        <v>-75</v>
+        <v>-35.9375</v>
       </c>
       <c r="C156" s="1">
         <v>-0.13159000000000001</v>
@@ -4349,7 +4349,7 @@
         <v>-75</v>
       </c>
       <c r="G156">
-        <v>-0.13167999999999999</v>
+        <v>-0.13170999999999999</v>
       </c>
       <c r="H156">
         <v>-75</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>-0.13435</v>
+        <v>0</v>
       </c>
       <c r="B157">
-        <v>-76.5625</v>
+        <v>-37.5</v>
       </c>
       <c r="C157" s="1">
         <v>-0.13435</v>
@@ -4375,7 +4375,7 @@
         <v>-76.5625</v>
       </c>
       <c r="G157">
-        <v>-0.13439000000000001</v>
+        <v>-0.13436999999999999</v>
       </c>
       <c r="H157">
         <v>-76.5625</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>-0.13711000000000001</v>
+        <v>0</v>
       </c>
       <c r="B158">
-        <v>-78.125</v>
+        <v>-39.0625</v>
       </c>
       <c r="C158">
         <v>-0.13711000000000001</v>
@@ -4401,7 +4401,7 @@
         <v>-78.125</v>
       </c>
       <c r="G158">
-        <v>-0.13714999999999999</v>
+        <v>-0.13716</v>
       </c>
       <c r="H158">
         <v>-78.125</v>
@@ -4409,10 +4409,10 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>-0.13986000000000001</v>
+        <v>0</v>
       </c>
       <c r="B159">
-        <v>-79.6875</v>
+        <v>-40.625</v>
       </c>
       <c r="C159">
         <v>-0.13983999999999999</v>
@@ -4435,10 +4435,10 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>-0.13954</v>
+        <v>0</v>
       </c>
       <c r="B160">
-        <v>-79.6875</v>
+        <v>-42.1875</v>
       </c>
       <c r="C160">
         <v>-0.13943</v>
@@ -4453,7 +4453,7 @@
         <v>-79.6875</v>
       </c>
       <c r="G160">
-        <v>-0.13950000000000001</v>
+        <v>-0.1394</v>
       </c>
       <c r="H160">
         <v>-79.6875</v>
@@ -4461,10 +4461,10 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>-0.1368</v>
+        <v>0</v>
       </c>
       <c r="B161">
-        <v>-78.125</v>
+        <v>-43.75</v>
       </c>
       <c r="C161">
         <v>-0.13668</v>
@@ -4479,7 +4479,7 @@
         <v>-78.125</v>
       </c>
       <c r="G161">
-        <v>-0.13675999999999999</v>
+        <v>-0.13674</v>
       </c>
       <c r="H161">
         <v>-78.125</v>
@@ -4487,10 +4487,10 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>-0.13403000000000001</v>
+        <v>0</v>
       </c>
       <c r="B162">
-        <v>-76.5625</v>
+        <v>-45.3125</v>
       </c>
       <c r="C162" s="1">
         <v>-0.13394</v>
@@ -4512,11 +4512,11 @@
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163">
-        <v>-0.13128999999999999</v>
+      <c r="A163" s="1">
+        <v>-1.0767E-4</v>
       </c>
       <c r="B163">
-        <v>-75</v>
+        <v>-46.875</v>
       </c>
       <c r="C163">
         <v>-0.13120999999999999</v>
@@ -4531,7 +4531,7 @@
         <v>-75</v>
       </c>
       <c r="G163">
-        <v>-0.13127</v>
+        <v>-0.13125000000000001</v>
       </c>
       <c r="H163">
         <v>-75</v>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>-0.12856000000000001</v>
+        <v>-8.3750000000000005E-2</v>
       </c>
       <c r="B164">
-        <v>-73.4375</v>
+        <v>-48.4375</v>
       </c>
       <c r="C164">
         <v>-0.12845000000000001</v>
@@ -4557,7 +4557,7 @@
         <v>-73.4375</v>
       </c>
       <c r="G164">
-        <v>-0.12851000000000001</v>
+        <v>-0.12852</v>
       </c>
       <c r="H164">
         <v>-73.4375</v>
@@ -4565,10 +4565,10 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>-0.1258</v>
+        <v>-8.7660000000000002E-2</v>
       </c>
       <c r="B165">
-        <v>-71.875</v>
+        <v>-50</v>
       </c>
       <c r="C165">
         <v>-0.12569</v>
@@ -4583,7 +4583,7 @@
         <v>-71.875</v>
       </c>
       <c r="G165">
-        <v>-0.12578</v>
+        <v>-0.12576000000000001</v>
       </c>
       <c r="H165">
         <v>-71.875</v>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>-0.12304</v>
+        <v>-9.042E-2</v>
       </c>
       <c r="B166">
-        <v>-70.3125</v>
+        <v>-51.5625</v>
       </c>
       <c r="C166">
         <v>-0.12298000000000001</v>
@@ -4609,7 +4609,7 @@
         <v>-70.3125</v>
       </c>
       <c r="G166">
-        <v>-0.12302</v>
+        <v>-0.12300999999999999</v>
       </c>
       <c r="H166">
         <v>-70.3125</v>
@@ -4617,10 +4617,10 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>-0.12033000000000001</v>
+        <v>-9.3160000000000007E-2</v>
       </c>
       <c r="B167">
-        <v>-68.75</v>
+        <v>-53.125</v>
       </c>
       <c r="C167">
         <v>-0.12021999999999999</v>
@@ -4629,7 +4629,7 @@
         <v>-68.75</v>
       </c>
       <c r="E167">
-        <v>-0.12028999999999999</v>
+        <v>-0.12028</v>
       </c>
       <c r="F167">
         <v>-68.75</v>
@@ -4643,10 +4643,10 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>-0.11755</v>
+        <v>-9.5909999999999995E-2</v>
       </c>
       <c r="B168">
-        <v>-67.1875</v>
+        <v>-54.6875</v>
       </c>
       <c r="C168">
         <v>-0.11749</v>
@@ -4655,7 +4655,7 @@
         <v>-67.1875</v>
       </c>
       <c r="E168">
-        <v>-0.11758</v>
+        <v>-0.11761000000000001</v>
       </c>
       <c r="F168">
         <v>-67.1875</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>-0.11482000000000001</v>
+        <v>-9.8650000000000002E-2</v>
       </c>
       <c r="B169">
-        <v>-65.625</v>
+        <v>-56.25</v>
       </c>
       <c r="C169">
         <v>-0.11473</v>
@@ -4687,7 +4687,7 @@
         <v>-65.625</v>
       </c>
       <c r="G169">
-        <v>-0.11482000000000001</v>
+        <v>-0.11481</v>
       </c>
       <c r="H169">
         <v>-65.625</v>
@@ -4695,10 +4695,10 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>-0.11206000000000001</v>
+        <v>-0.1014</v>
       </c>
       <c r="B170">
-        <v>-64.0625</v>
+        <v>-57.8125</v>
       </c>
       <c r="C170">
         <v>-0.11201999999999999</v>
@@ -4713,7 +4713,7 @@
         <v>-64.0625</v>
       </c>
       <c r="G170">
-        <v>-0.11208</v>
+        <v>-0.11207</v>
       </c>
       <c r="H170">
         <v>-64.0625</v>
@@ -4721,10 +4721,10 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>-0.10931</v>
+        <v>-0.10414</v>
       </c>
       <c r="B171">
-        <v>-62.5</v>
+        <v>-59.375</v>
       </c>
       <c r="C171">
         <v>-0.10924</v>
@@ -4739,7 +4739,7 @@
         <v>-62.5</v>
       </c>
       <c r="G171">
-        <v>-0.10933</v>
+        <v>-0.10935</v>
       </c>
       <c r="H171">
         <v>-62.5</v>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>-0.10657</v>
+        <v>-0.10689</v>
       </c>
       <c r="B172">
         <v>-60.9375</v>
@@ -4765,7 +4765,7 @@
         <v>-60.9375</v>
       </c>
       <c r="G172">
-        <v>-0.10659</v>
+        <v>-0.10661</v>
       </c>
       <c r="H172">
         <v>-60.9375</v>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>-0.10384</v>
+        <v>-0.10963000000000001</v>
       </c>
       <c r="B173">
-        <v>-59.375</v>
+        <v>-62.5</v>
       </c>
       <c r="C173">
         <v>-0.10375</v>
@@ -4791,7 +4791,7 @@
         <v>-59.375</v>
       </c>
       <c r="G173">
-        <v>-0.10384</v>
+        <v>-0.10385</v>
       </c>
       <c r="H173">
         <v>-59.375</v>
@@ -4799,10 +4799,10 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>-0.10108</v>
+        <v>-0.11239</v>
       </c>
       <c r="B174">
-        <v>-57.8125</v>
+        <v>-64.0625</v>
       </c>
       <c r="C174">
         <v>-0.10102</v>
@@ -4825,10 +4825,10 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>-9.8350000000000007E-2</v>
+        <v>-0.11514000000000001</v>
       </c>
       <c r="B175">
-        <v>-56.25</v>
+        <v>-65.625</v>
       </c>
       <c r="C175">
         <v>-9.8299999999999998E-2</v>
@@ -4843,7 +4843,7 @@
         <v>-56.25</v>
       </c>
       <c r="G175">
-        <v>-9.8390000000000005E-2</v>
+        <v>-9.8360000000000003E-2</v>
       </c>
       <c r="H175">
         <v>-56.25</v>
@@ -4851,10 +4851,10 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>-9.5589999999999994E-2</v>
+        <v>-0.11788</v>
       </c>
       <c r="B176">
-        <v>-54.6875</v>
+        <v>-67.1875</v>
       </c>
       <c r="C176">
         <v>-9.5570000000000002E-2</v>
@@ -4869,7 +4869,7 @@
         <v>-54.6875</v>
       </c>
       <c r="G176">
-        <v>-9.5610000000000001E-2</v>
+        <v>-9.5649999999999999E-2</v>
       </c>
       <c r="H176">
         <v>-54.6875</v>
@@ -4877,10 +4877,10 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>-9.2850000000000002E-2</v>
+        <v>-0.12063</v>
       </c>
       <c r="B177">
-        <v>-53.125</v>
+        <v>-68.75</v>
       </c>
       <c r="C177">
         <v>-9.2810000000000004E-2</v>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>-9.0120000000000006E-2</v>
+        <v>-0.12339</v>
       </c>
       <c r="B178">
-        <v>-51.5625</v>
+        <v>-70.3125</v>
       </c>
       <c r="C178">
         <v>-9.01E-2</v>
@@ -4921,7 +4921,7 @@
         <v>-51.5625</v>
       </c>
       <c r="G178">
-        <v>-9.0160000000000004E-2</v>
+        <v>-9.0179999999999996E-2</v>
       </c>
       <c r="H178">
         <v>-51.5625</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>-8.7279999999999996E-2</v>
+        <v>-0.12612000000000001</v>
       </c>
       <c r="B179">
-        <v>-50</v>
+        <v>-71.875</v>
       </c>
       <c r="C179">
         <v>-8.7260000000000004E-2</v>
@@ -4941,7 +4941,7 @@
         <v>-50</v>
       </c>
       <c r="E179">
-        <v>-8.7340000000000001E-2</v>
+        <v>-8.7349999999999997E-2</v>
       </c>
       <c r="F179">
         <v>-50</v>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>-8.4540000000000004E-2</v>
+        <v>-0.12887999999999999</v>
       </c>
       <c r="B180">
-        <v>-48.4375</v>
+        <v>-73.4375</v>
       </c>
       <c r="C180">
         <v>-8.4519999999999998E-2</v>
@@ -4973,7 +4973,7 @@
         <v>-48.4375</v>
       </c>
       <c r="G180">
-        <v>-8.4610000000000005E-2</v>
+        <v>-8.4620000000000001E-2</v>
       </c>
       <c r="H180">
         <v>-48.4375</v>
@@ -4981,10 +4981,10 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>-8.1790000000000002E-2</v>
+        <v>-0.13161999999999999</v>
       </c>
       <c r="B181">
-        <v>-46.875</v>
+        <v>-75</v>
       </c>
       <c r="C181">
         <v>-8.1759999999999999E-2</v>
@@ -4993,7 +4993,7 @@
         <v>-46.875</v>
       </c>
       <c r="E181">
-        <v>-8.1869999999999998E-2</v>
+        <v>-8.1879999999999994E-2</v>
       </c>
       <c r="F181">
         <v>-46.875</v>
@@ -5007,10 +5007,10 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>-7.9030000000000003E-2</v>
+        <v>-0.13435</v>
       </c>
       <c r="B182">
-        <v>-45.3125</v>
+        <v>-76.5625</v>
       </c>
       <c r="C182">
         <v>-7.9049999999999995E-2</v>
@@ -5025,7 +5025,7 @@
         <v>-45.3125</v>
       </c>
       <c r="G182">
-        <v>-7.9140000000000002E-2</v>
+        <v>-7.9149999999999998E-2</v>
       </c>
       <c r="H182">
         <v>-45.3125</v>
@@ -5033,10 +5033,10 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>-7.6289999999999997E-2</v>
+        <v>-0.13711000000000001</v>
       </c>
       <c r="B183">
-        <v>-43.75</v>
+        <v>-78.125</v>
       </c>
       <c r="C183">
         <v>-7.6289999999999997E-2</v>
@@ -5051,7 +5051,7 @@
         <v>-43.75</v>
       </c>
       <c r="G183">
-        <v>-7.6380000000000003E-2</v>
+        <v>-7.6359999999999997E-2</v>
       </c>
       <c r="H183">
         <v>-43.75</v>
@@ -5059,10 +5059,10 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>-7.356E-2</v>
+        <v>-0.13986000000000001</v>
       </c>
       <c r="B184">
-        <v>-42.1875</v>
+        <v>-79.6875</v>
       </c>
       <c r="C184">
         <v>-7.356E-2</v>
@@ -5077,7 +5077,7 @@
         <v>-42.1875</v>
       </c>
       <c r="G184">
-        <v>-7.3669999999999999E-2</v>
+        <v>-7.3679999999999995E-2</v>
       </c>
       <c r="H184">
         <v>-42.1875</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>-7.0800000000000002E-2</v>
+        <v>-0.1426</v>
       </c>
       <c r="B185">
-        <v>-40.625</v>
+        <v>-81.25</v>
       </c>
       <c r="C185">
         <v>-7.0830000000000004E-2</v>
@@ -5103,7 +5103,7 @@
         <v>-40.625</v>
       </c>
       <c r="G185">
-        <v>-7.0910000000000001E-2</v>
+        <v>-7.0919999999999997E-2</v>
       </c>
       <c r="H185">
         <v>-40.625</v>
@@ -5111,10 +5111,10 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>-6.8070000000000006E-2</v>
+        <v>-0.14538000000000001</v>
       </c>
       <c r="B186">
-        <v>-39.0625</v>
+        <v>-82.8125</v>
       </c>
       <c r="C186">
         <v>-6.8089999999999998E-2</v>
@@ -5129,7 +5129,7 @@
         <v>-39.0625</v>
       </c>
       <c r="G186">
-        <v>-6.8180000000000004E-2</v>
+        <v>-6.8169999999999994E-2</v>
       </c>
       <c r="H186">
         <v>-39.0625</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>-6.5310000000000007E-2</v>
+        <v>-0.14810999999999999</v>
       </c>
       <c r="B187">
-        <v>-37.5</v>
+        <v>-84.375</v>
       </c>
       <c r="C187">
         <v>-6.5360000000000001E-2</v>
@@ -5149,7 +5149,7 @@
         <v>-37.5</v>
       </c>
       <c r="E187">
-        <v>-6.5439999999999998E-2</v>
+        <v>-6.5420000000000006E-2</v>
       </c>
       <c r="F187">
         <v>-37.5</v>
@@ -5163,10 +5163,10 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>-6.2579999999999997E-2</v>
+        <v>-0.15087</v>
       </c>
       <c r="B188">
-        <v>-35.9375</v>
+        <v>-85.9375</v>
       </c>
       <c r="C188">
         <v>-6.2619999999999995E-2</v>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>-5.9819999999999998E-2</v>
+        <v>-0.15362000000000001</v>
       </c>
       <c r="B189">
-        <v>-34.375</v>
+        <v>-87.5</v>
       </c>
       <c r="C189">
         <v>-5.9889999999999999E-2</v>
@@ -5207,7 +5207,7 @@
         <v>-34.375</v>
       </c>
       <c r="G189">
-        <v>-5.9929999999999997E-2</v>
+        <v>-5.9909999999999998E-2</v>
       </c>
       <c r="H189">
         <v>-34.375</v>
@@ -5215,10 +5215,10 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>-5.706E-2</v>
+        <v>-0.15636</v>
       </c>
       <c r="B190">
-        <v>-32.8125</v>
+        <v>-89.0625</v>
       </c>
       <c r="C190">
         <v>-5.7149999999999999E-2</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>-5.4179999999999999E-2</v>
+        <v>-0.15914</v>
       </c>
       <c r="B191">
-        <v>-31.25</v>
+        <v>-90.625</v>
       </c>
       <c r="C191">
         <v>-5.4420000000000003E-2</v>
@@ -5259,7 +5259,7 @@
         <v>-31.25</v>
       </c>
       <c r="G191">
-        <v>-5.4480000000000001E-2</v>
+        <v>-5.4489999999999997E-2</v>
       </c>
       <c r="H191">
         <v>-31.25</v>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>-5.0650000000000001E-2</v>
+        <v>-0.16189000000000001</v>
       </c>
       <c r="B192">
-        <v>-29.6875</v>
+        <v>-92.1875</v>
       </c>
       <c r="C192">
         <v>-5.1659999999999998E-2</v>
@@ -5285,7 +5285,7 @@
         <v>-29.6875</v>
       </c>
       <c r="G192">
-        <v>-5.1720000000000002E-2</v>
+        <v>-5.1729999999999998E-2</v>
       </c>
       <c r="H192">
         <v>-29.6875</v>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>-4.5289999999999997E-2</v>
+        <v>-0.16464999999999999</v>
       </c>
       <c r="B193">
-        <v>-28.125</v>
+        <v>-93.75</v>
       </c>
       <c r="C193">
         <v>-4.8930000000000001E-2</v>
@@ -5311,7 +5311,7 @@
         <v>-28.125</v>
       </c>
       <c r="G193">
-        <v>-4.8989999999999999E-2</v>
+        <v>-4.895E-2</v>
       </c>
       <c r="H193">
         <v>-28.125</v>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>-3.6799999999999999E-2</v>
+        <v>-0.16739999999999999</v>
       </c>
       <c r="B194">
-        <v>-26.5625</v>
+        <v>-95.3125</v>
       </c>
       <c r="C194">
         <v>-4.6149999999999997E-2</v>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>-5.1000000000000004E-3</v>
+        <v>-0.17016000000000001</v>
       </c>
       <c r="B195">
-        <v>-25</v>
+        <v>-96.875</v>
       </c>
       <c r="C195">
         <v>-4.326E-2</v>
@@ -5363,7 +5363,7 @@
         <v>-25</v>
       </c>
       <c r="G195">
-        <v>-4.3499999999999997E-2</v>
+        <v>-4.3479999999999998E-2</v>
       </c>
       <c r="H195">
         <v>-25</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>0</v>
+        <v>-0.17294000000000001</v>
       </c>
       <c r="B196">
-        <v>-23.4375</v>
+        <v>-98.4375</v>
       </c>
       <c r="C196">
         <v>-3.9789999999999999E-2</v>
@@ -5389,7 +5389,7 @@
         <v>-23.4375</v>
       </c>
       <c r="G196">
-        <v>-4.0739999999999998E-2</v>
+        <v>-4.0759999999999998E-2</v>
       </c>
       <c r="H196">
         <v>-23.4375</v>
@@ -5397,10 +5397,10 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>0</v>
+        <v>-0.17533000000000001</v>
       </c>
       <c r="B197">
-        <v>-21.875</v>
+        <v>-100</v>
       </c>
       <c r="C197">
         <v>-3.5380000000000002E-2</v>
@@ -5415,7 +5415,7 @@
         <v>-21.875</v>
       </c>
       <c r="G197">
-        <v>-3.7859999999999998E-2</v>
+        <v>-3.7879999999999997E-2</v>
       </c>
       <c r="H197">
         <v>-21.875</v>
@@ -5423,10 +5423,10 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>0</v>
+        <v>-0.17257</v>
       </c>
       <c r="B198">
-        <v>-20.3125</v>
+        <v>-98.4375</v>
       </c>
       <c r="C198">
         <v>-2.972E-2</v>
@@ -5441,7 +5441,7 @@
         <v>-20.3125</v>
       </c>
       <c r="G198">
-        <v>-3.456E-2</v>
+        <v>-3.4549999999999997E-2</v>
       </c>
       <c r="H198">
         <v>-20.3125</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>0</v>
+        <v>-0.16982</v>
       </c>
       <c r="B199">
-        <v>-18.75</v>
+        <v>-96.875</v>
       </c>
       <c r="C199">
         <v>-2.196E-2</v>
@@ -5467,7 +5467,7 @@
         <v>-18.75</v>
       </c>
       <c r="G199">
-        <v>-3.0339999999999999E-2</v>
+        <v>-3.0360000000000002E-2</v>
       </c>
       <c r="H199">
         <v>-18.75</v>
@@ -5475,10 +5475,10 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>0</v>
+        <v>-0.16705999999999999</v>
       </c>
       <c r="B200">
-        <v>-17.1875</v>
+        <v>-95.3125</v>
       </c>
       <c r="C200" s="1">
         <v>-8.8289100000000001E-4</v>
@@ -5501,10 +5501,10 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>0</v>
+        <v>-0.1643</v>
       </c>
       <c r="B201">
-        <v>-15.625</v>
+        <v>-93.75</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>0</v>
+        <v>-0.16156999999999999</v>
       </c>
       <c r="B202">
-        <v>-14.0625</v>
+        <v>-92.1875</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -5553,10 +5553,10 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>0</v>
+        <v>-0.15878999999999999</v>
       </c>
       <c r="B203">
-        <v>-12.5</v>
+        <v>-90.625</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -5579,10 +5579,10 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>0</v>
+        <v>-0.15606</v>
       </c>
       <c r="B204">
-        <v>-10.9375</v>
+        <v>-89.0625</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -5605,10 +5605,10 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>0</v>
+        <v>-0.15329999999999999</v>
       </c>
       <c r="B205">
-        <v>-9.375</v>
+        <v>-87.5</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>0</v>
+        <v>-0.15054000000000001</v>
       </c>
       <c r="B206">
-        <v>-7.8125</v>
+        <v>-85.9375</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>0</v>
+        <v>-0.14779</v>
       </c>
       <c r="B207">
-        <v>-6.25</v>
+        <v>-84.375</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -5683,10 +5683,10 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>0</v>
+        <v>-0.14502999999999999</v>
       </c>
       <c r="B208">
-        <v>-4.6875</v>
+        <v>-82.8125</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -5709,10 +5709,10 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>0</v>
+        <v>-0.14230000000000001</v>
       </c>
       <c r="B209">
-        <v>-3.125</v>
+        <v>-81.25</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -5735,10 +5735,10 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>0</v>
+        <v>-0.13954</v>
       </c>
       <c r="B210">
-        <v>-1.5625</v>
+        <v>-79.6875</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -5756,6 +5756,406 @@
         <v>0</v>
       </c>
       <c r="H210">
+        <v>-1.5625</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>-0.1368</v>
+      </c>
+      <c r="B211">
+        <v>-78.125</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>-0.13403000000000001</v>
+      </c>
+      <c r="B212">
+        <v>-76.5625</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>-0.13128999999999999</v>
+      </c>
+      <c r="B213">
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>-0.12856000000000001</v>
+      </c>
+      <c r="B214">
+        <v>-73.4375</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>-0.1258</v>
+      </c>
+      <c r="B215">
+        <v>-71.875</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>-0.12304</v>
+      </c>
+      <c r="B216">
+        <v>-70.3125</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>-0.12033000000000001</v>
+      </c>
+      <c r="B217">
+        <v>-68.75</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>-0.11755</v>
+      </c>
+      <c r="B218">
+        <v>-67.1875</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>-0.11482000000000001</v>
+      </c>
+      <c r="B219">
+        <v>-65.625</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>-0.11206000000000001</v>
+      </c>
+      <c r="B220">
+        <v>-64.0625</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>-0.10931</v>
+      </c>
+      <c r="B221">
+        <v>-62.5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>-0.10657</v>
+      </c>
+      <c r="B222">
+        <v>-60.9375</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>-0.10384</v>
+      </c>
+      <c r="B223">
+        <v>-59.375</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>-0.10108</v>
+      </c>
+      <c r="B224">
+        <v>-57.8125</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>-9.8350000000000007E-2</v>
+      </c>
+      <c r="B225">
+        <v>-56.25</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>-9.5589999999999994E-2</v>
+      </c>
+      <c r="B226">
+        <v>-54.6875</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>-9.2850000000000002E-2</v>
+      </c>
+      <c r="B227">
+        <v>-53.125</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>-9.0120000000000006E-2</v>
+      </c>
+      <c r="B228">
+        <v>-51.5625</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>-8.7279999999999996E-2</v>
+      </c>
+      <c r="B229">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>-8.4540000000000004E-2</v>
+      </c>
+      <c r="B230">
+        <v>-48.4375</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>-8.1790000000000002E-2</v>
+      </c>
+      <c r="B231">
+        <v>-46.875</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>-7.9030000000000003E-2</v>
+      </c>
+      <c r="B232">
+        <v>-45.3125</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>-7.6289999999999997E-2</v>
+      </c>
+      <c r="B233">
+        <v>-43.75</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>-7.356E-2</v>
+      </c>
+      <c r="B234">
+        <v>-42.1875</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>-7.0800000000000002E-2</v>
+      </c>
+      <c r="B235">
+        <v>-40.625</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>-6.8070000000000006E-2</v>
+      </c>
+      <c r="B236">
+        <v>-39.0625</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>-6.5310000000000007E-2</v>
+      </c>
+      <c r="B237">
+        <v>-37.5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>-6.2579999999999997E-2</v>
+      </c>
+      <c r="B238">
+        <v>-35.9375</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>-5.9819999999999998E-2</v>
+      </c>
+      <c r="B239">
+        <v>-34.375</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>-5.706E-2</v>
+      </c>
+      <c r="B240">
+        <v>-32.8125</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>-5.4179999999999999E-2</v>
+      </c>
+      <c r="B241">
+        <v>-31.25</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>-5.0650000000000001E-2</v>
+      </c>
+      <c r="B242">
+        <v>-29.6875</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>-4.5289999999999997E-2</v>
+      </c>
+      <c r="B243">
+        <v>-28.125</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>-3.6799999999999999E-2</v>
+      </c>
+      <c r="B244">
+        <v>-26.5625</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>-5.1000000000000004E-3</v>
+      </c>
+      <c r="B245">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>0</v>
+      </c>
+      <c r="B246">
+        <v>-23.4375</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>0</v>
+      </c>
+      <c r="B247">
+        <v>-21.875</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>0</v>
+      </c>
+      <c r="B248">
+        <v>-20.3125</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>0</v>
+      </c>
+      <c r="B249">
+        <v>-18.75</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>0</v>
+      </c>
+      <c r="B250">
+        <v>-17.1875</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>0</v>
+      </c>
+      <c r="B251">
+        <v>-15.625</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>0</v>
+      </c>
+      <c r="B252">
+        <v>-14.0625</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>0</v>
+      </c>
+      <c r="B253">
+        <v>-12.5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>0</v>
+      </c>
+      <c r="B254">
+        <v>-10.9375</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>0</v>
+      </c>
+      <c r="B255">
+        <v>-9.375</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>0</v>
+      </c>
+      <c r="B256">
+        <v>-7.8125</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>0</v>
+      </c>
+      <c r="B257">
+        <v>-6.25</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>0</v>
+      </c>
+      <c r="B258">
+        <v>-4.6875</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>0</v>
+      </c>
+      <c r="B259">
+        <v>-3.125</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>0</v>
+      </c>
+      <c r="B260">
         <v>-1.5625</v>
       </c>
     </row>
